--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22590" uniqueCount="1679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22590" uniqueCount="1677">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T14:29:25+02:00</t>
+    <t>2026-10-14T17:02:42+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3259,13 +3259,6 @@
   </si>
   <si>
     <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
-</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
 </t>
   </si>
   <si>
@@ -6258,7 +6251,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="109">
@@ -6266,7 +6259,7 @@
         <v>4</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="110">
@@ -6282,7 +6275,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="112">
@@ -6290,7 +6283,7 @@
         <v>9</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="113">
@@ -6312,7 +6305,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="116">
@@ -6344,7 +6337,7 @@
         <v>22</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="120">
@@ -6388,7 +6381,7 @@
         <v>32</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="126">
@@ -44482,7 +44475,7 @@
         <v>77</v>
       </c>
       <c r="AJ364" t="s" s="2">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="AK364" t="s" s="2">
         <v>80</v>
@@ -44519,7 +44512,7 @@
         <v>21</v>
       </c>
       <c r="L365" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="M365" t="s" s="2">
         <v>84</v>
@@ -44585,7 +44578,7 @@
         <v>82</v>
       </c>
       <c r="AJ365" t="s" s="2">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="AK365" t="s" s="2">
         <v>21</v>
@@ -44836,7 +44829,7 @@
         <v>101</v>
       </c>
       <c r="N368" t="s" s="2">
-        <v>1044</v>
+        <v>102</v>
       </c>
       <c r="O368" s="2"/>
       <c r="P368" s="2"/>
@@ -44896,7 +44889,7 @@
         <v>82</v>
       </c>
       <c r="AJ368" t="s" s="2">
-        <v>1045</v>
+        <v>21</v>
       </c>
       <c r="AK368" t="s" s="2">
         <v>103</v>
@@ -44907,10 +44900,10 @@
         <v>979</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -45014,10 +45007,10 @@
         <v>979</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -45043,14 +45036,14 @@
         <v>222</v>
       </c>
       <c r="M370" t="s" s="2">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="N370" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O370" s="2"/>
       <c r="P370" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q370" t="s" s="2">
         <v>21</v>
@@ -45087,10 +45080,10 @@
         <v>21</v>
       </c>
       <c r="AC370" t="s" s="2">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="AD370" t="s" s="2">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="AE370" t="s" s="2">
         <v>21</v>
@@ -45099,7 +45092,7 @@
         <v>92</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH370" t="s" s="2">
         <v>76</v>
@@ -45119,10 +45112,10 @@
         <v>979</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -45222,10 +45215,10 @@
         <v>979</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -45327,10 +45320,10 @@
         <v>979</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -45434,10 +45427,10 @@
         <v>979</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -45501,7 +45494,7 @@
       </c>
       <c r="Z374" s="2"/>
       <c r="AA374" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB374" t="s" s="2">
         <v>21</v>
@@ -45539,10 +45532,10 @@
         <v>979</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -45646,10 +45639,10 @@
         <v>979</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -45751,10 +45744,10 @@
         <v>979</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -45854,10 +45847,10 @@
         <v>979</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -45959,13 +45952,13 @@
         <v>979</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E379" t="s" s="2">
         <v>21</v>
@@ -45990,14 +45983,14 @@
         <v>222</v>
       </c>
       <c r="M379" t="s" s="2">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="N379" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O379" s="2"/>
       <c r="P379" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q379" t="s" s="2">
         <v>21</v>
@@ -46046,7 +46039,7 @@
         <v>21</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>76</v>
@@ -46066,10 +46059,10 @@
         <v>979</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -46169,10 +46162,10 @@
         <v>979</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -46274,10 +46267,10 @@
         <v>979</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -46322,7 +46315,7 @@
         <v>21</v>
       </c>
       <c r="T382" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="U382" t="s" s="2">
         <v>21</v>
@@ -46381,10 +46374,10 @@
         <v>979</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -46429,7 +46422,7 @@
         <v>21</v>
       </c>
       <c r="T383" t="s" s="2">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="U383" t="s" s="2">
         <v>21</v>
@@ -46448,7 +46441,7 @@
       </c>
       <c r="Z383" s="2"/>
       <c r="AA383" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB383" t="s" s="2">
         <v>21</v>
@@ -46486,10 +46479,10 @@
         <v>979</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -46589,10 +46582,10 @@
         <v>979</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -46694,10 +46687,10 @@
         <v>979</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -46723,16 +46716,16 @@
         <v>165</v>
       </c>
       <c r="M386" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N386" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O386" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N386" t="s" s="2">
+      <c r="P386" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O386" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P386" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q386" t="s" s="2">
         <v>21</v>
@@ -46781,7 +46774,7 @@
         <v>21</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>76</v>
@@ -46801,10 +46794,10 @@
         <v>979</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -46904,10 +46897,10 @@
         <v>979</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -47009,10 +47002,10 @@
         <v>979</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -47116,10 +47109,10 @@
         <v>979</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -47221,10 +47214,10 @@
         <v>979</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -47326,10 +47319,10 @@
         <v>979</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
@@ -47431,10 +47424,10 @@
         <v>979</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -47538,10 +47531,10 @@
         <v>979</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -47567,16 +47560,16 @@
         <v>83</v>
       </c>
       <c r="M394" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N394" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O394" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N394" t="s" s="2">
+      <c r="P394" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O394" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P394" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q394" t="s" s="2">
         <v>21</v>
@@ -47625,7 +47618,7 @@
         <v>21</v>
       </c>
       <c r="AG394" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH394" t="s" s="2">
         <v>76</v>
@@ -47645,10 +47638,10 @@
         <v>979</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -47693,7 +47686,7 @@
         <v>21</v>
       </c>
       <c r="T395" t="s" s="2">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="U395" t="s" s="2">
         <v>253</v>
@@ -47752,10 +47745,10 @@
         <v>979</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -47857,10 +47850,10 @@
         <v>979</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -47960,10 +47953,10 @@
         <v>979</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
@@ -48065,13 +48058,13 @@
         <v>979</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D399" t="s" s="2">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E399" t="s" s="2">
         <v>21</v>
@@ -48096,14 +48089,14 @@
         <v>222</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="N399" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O399" s="2"/>
       <c r="P399" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q399" t="s" s="2">
         <v>21</v>
@@ -48152,7 +48145,7 @@
         <v>21</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>76</v>
@@ -48172,10 +48165,10 @@
         <v>979</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
@@ -48275,10 +48268,10 @@
         <v>979</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" t="s" s="2">
@@ -48380,10 +48373,10 @@
         <v>979</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -48428,7 +48421,7 @@
         <v>21</v>
       </c>
       <c r="T402" t="s" s="2">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="U402" t="s" s="2">
         <v>21</v>
@@ -48487,10 +48480,10 @@
         <v>979</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -48519,7 +48512,7 @@
         <v>239</v>
       </c>
       <c r="N403" t="s" s="2">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="O403" t="s" s="2">
         <v>241</v>
@@ -48535,7 +48528,7 @@
         <v>21</v>
       </c>
       <c r="T403" t="s" s="2">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="U403" t="s" s="2">
         <v>21</v>
@@ -48554,7 +48547,7 @@
       </c>
       <c r="Z403" s="2"/>
       <c r="AA403" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB403" t="s" s="2">
         <v>21</v>
@@ -48592,10 +48585,10 @@
         <v>979</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -48640,7 +48633,7 @@
         <v>21</v>
       </c>
       <c r="T404" t="s" s="2">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="U404" t="s" s="2">
         <v>253</v>
@@ -48699,10 +48692,10 @@
         <v>979</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -48804,10 +48797,10 @@
         <v>979</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -48907,10 +48900,10 @@
         <v>979</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -49012,13 +49005,13 @@
         <v>979</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D408" t="s" s="2">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="E408" t="s" s="2">
         <v>21</v>
@@ -49043,14 +49036,14 @@
         <v>222</v>
       </c>
       <c r="M408" t="s" s="2">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="N408" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O408" s="2"/>
       <c r="P408" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q408" t="s" s="2">
         <v>21</v>
@@ -49099,7 +49092,7 @@
         <v>21</v>
       </c>
       <c r="AG408" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH408" t="s" s="2">
         <v>76</v>
@@ -49119,10 +49112,10 @@
         <v>979</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D409" s="2"/>
       <c r="E409" t="s" s="2">
@@ -49222,10 +49215,10 @@
         <v>979</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -49327,10 +49320,10 @@
         <v>979</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -49375,7 +49368,7 @@
         <v>21</v>
       </c>
       <c r="T411" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="U411" t="s" s="2">
         <v>21</v>
@@ -49434,10 +49427,10 @@
         <v>979</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -49466,7 +49459,7 @@
         <v>239</v>
       </c>
       <c r="N412" t="s" s="2">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="O412" t="s" s="2">
         <v>241</v>
@@ -49482,7 +49475,7 @@
         <v>21</v>
       </c>
       <c r="T412" t="s" s="2">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="U412" t="s" s="2">
         <v>21</v>
@@ -49501,7 +49494,7 @@
       </c>
       <c r="Z412" s="2"/>
       <c r="AA412" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB412" t="s" s="2">
         <v>21</v>
@@ -49539,10 +49532,10 @@
         <v>979</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -49587,7 +49580,7 @@
         <v>21</v>
       </c>
       <c r="T413" t="s" s="2">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="U413" t="s" s="2">
         <v>253</v>
@@ -49646,10 +49639,10 @@
         <v>979</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -49751,10 +49744,10 @@
         <v>979</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -49854,10 +49847,10 @@
         <v>979</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -49959,13 +49952,13 @@
         <v>979</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="E417" t="s" s="2">
         <v>21</v>
@@ -49990,14 +49983,14 @@
         <v>222</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="N417" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O417" s="2"/>
       <c r="P417" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q417" t="s" s="2">
         <v>21</v>
@@ -50046,7 +50039,7 @@
         <v>21</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>76</v>
@@ -50066,10 +50059,10 @@
         <v>979</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -50169,10 +50162,10 @@
         <v>979</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -50274,10 +50267,10 @@
         <v>979</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -50322,7 +50315,7 @@
         <v>21</v>
       </c>
       <c r="T420" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="U420" t="s" s="2">
         <v>21</v>
@@ -50381,10 +50374,10 @@
         <v>979</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -50413,7 +50406,7 @@
         <v>239</v>
       </c>
       <c r="N421" t="s" s="2">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="O421" t="s" s="2">
         <v>241</v>
@@ -50429,7 +50422,7 @@
         <v>21</v>
       </c>
       <c r="T421" t="s" s="2">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="U421" t="s" s="2">
         <v>21</v>
@@ -50448,7 +50441,7 @@
       </c>
       <c r="Z421" s="2"/>
       <c r="AA421" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB421" t="s" s="2">
         <v>21</v>
@@ -50486,10 +50479,10 @@
         <v>979</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -50534,7 +50527,7 @@
         <v>21</v>
       </c>
       <c r="T422" t="s" s="2">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="U422" t="s" s="2">
         <v>253</v>
@@ -50593,10 +50586,10 @@
         <v>979</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -50698,10 +50691,10 @@
         <v>979</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -50801,10 +50794,10 @@
         <v>979</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -50906,13 +50899,13 @@
         <v>979</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D426" t="s" s="2">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="E426" t="s" s="2">
         <v>21</v>
@@ -50937,14 +50930,14 @@
         <v>222</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="N426" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O426" s="2"/>
       <c r="P426" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q426" t="s" s="2">
         <v>21</v>
@@ -50993,7 +50986,7 @@
         <v>21</v>
       </c>
       <c r="AG426" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH426" t="s" s="2">
         <v>76</v>
@@ -51013,10 +51006,10 @@
         <v>979</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" t="s" s="2">
@@ -51116,10 +51109,10 @@
         <v>979</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -51221,10 +51214,10 @@
         <v>979</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -51269,7 +51262,7 @@
         <v>21</v>
       </c>
       <c r="T429" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="U429" t="s" s="2">
         <v>21</v>
@@ -51328,10 +51321,10 @@
         <v>979</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -51360,7 +51353,7 @@
         <v>239</v>
       </c>
       <c r="N430" t="s" s="2">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="O430" t="s" s="2">
         <v>241</v>
@@ -51376,7 +51369,7 @@
         <v>21</v>
       </c>
       <c r="T430" t="s" s="2">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="U430" t="s" s="2">
         <v>21</v>
@@ -51395,7 +51388,7 @@
       </c>
       <c r="Z430" s="2"/>
       <c r="AA430" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB430" t="s" s="2">
         <v>21</v>
@@ -51433,10 +51426,10 @@
         <v>979</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -51481,7 +51474,7 @@
         <v>21</v>
       </c>
       <c r="T431" t="s" s="2">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="U431" t="s" s="2">
         <v>253</v>
@@ -51540,10 +51533,10 @@
         <v>979</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -51645,10 +51638,10 @@
         <v>979</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -51748,10 +51741,10 @@
         <v>979</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -51853,13 +51846,13 @@
         <v>979</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D435" t="s" s="2">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E435" t="s" s="2">
         <v>21</v>
@@ -51884,14 +51877,14 @@
         <v>222</v>
       </c>
       <c r="M435" t="s" s="2">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="N435" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O435" s="2"/>
       <c r="P435" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q435" t="s" s="2">
         <v>21</v>
@@ -51940,7 +51933,7 @@
         <v>21</v>
       </c>
       <c r="AG435" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH435" t="s" s="2">
         <v>76</v>
@@ -51960,10 +51953,10 @@
         <v>979</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -52063,10 +52056,10 @@
         <v>979</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -52168,10 +52161,10 @@
         <v>979</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -52216,7 +52209,7 @@
         <v>21</v>
       </c>
       <c r="T438" t="s" s="2">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="U438" t="s" s="2">
         <v>21</v>
@@ -52275,10 +52268,10 @@
         <v>979</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" t="s" s="2">
@@ -52307,7 +52300,7 @@
         <v>239</v>
       </c>
       <c r="N439" t="s" s="2">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="O439" t="s" s="2">
         <v>241</v>
@@ -52323,7 +52316,7 @@
         <v>21</v>
       </c>
       <c r="T439" t="s" s="2">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="U439" t="s" s="2">
         <v>21</v>
@@ -52342,7 +52335,7 @@
       </c>
       <c r="Z439" s="2"/>
       <c r="AA439" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB439" t="s" s="2">
         <v>21</v>
@@ -52380,10 +52373,10 @@
         <v>979</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" t="s" s="2">
@@ -52428,7 +52421,7 @@
         <v>21</v>
       </c>
       <c r="T440" t="s" s="2">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="U440" t="s" s="2">
         <v>253</v>
@@ -52487,10 +52480,10 @@
         <v>979</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" t="s" s="2">
@@ -52592,10 +52585,10 @@
         <v>979</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -52695,10 +52688,10 @@
         <v>979</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -52800,13 +52793,13 @@
         <v>979</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D444" t="s" s="2">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="E444" t="s" s="2">
         <v>21</v>
@@ -52831,14 +52824,14 @@
         <v>222</v>
       </c>
       <c r="M444" t="s" s="2">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="N444" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O444" s="2"/>
       <c r="P444" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q444" t="s" s="2">
         <v>21</v>
@@ -52887,7 +52880,7 @@
         <v>21</v>
       </c>
       <c r="AG444" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH444" t="s" s="2">
         <v>76</v>
@@ -52907,10 +52900,10 @@
         <v>979</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -53010,10 +53003,10 @@
         <v>979</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" t="s" s="2">
@@ -53115,10 +53108,10 @@
         <v>979</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" t="s" s="2">
@@ -53163,7 +53156,7 @@
         <v>21</v>
       </c>
       <c r="T447" t="s" s="2">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="U447" t="s" s="2">
         <v>21</v>
@@ -53222,10 +53215,10 @@
         <v>979</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
@@ -53270,7 +53263,7 @@
         <v>21</v>
       </c>
       <c r="T448" t="s" s="2">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="U448" t="s" s="2">
         <v>21</v>
@@ -53289,7 +53282,7 @@
       </c>
       <c r="Z448" s="2"/>
       <c r="AA448" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB448" t="s" s="2">
         <v>21</v>
@@ -53327,10 +53320,10 @@
         <v>979</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
@@ -53375,7 +53368,7 @@
         <v>21</v>
       </c>
       <c r="T449" t="s" s="2">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="U449" t="s" s="2">
         <v>253</v>
@@ -53434,10 +53427,10 @@
         <v>979</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
@@ -53539,10 +53532,10 @@
         <v>979</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" t="s" s="2">
@@ -53642,10 +53635,10 @@
         <v>979</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -53747,13 +53740,13 @@
         <v>979</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D453" t="s" s="2">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E453" t="s" s="2">
         <v>21</v>
@@ -53778,14 +53771,14 @@
         <v>222</v>
       </c>
       <c r="M453" t="s" s="2">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="N453" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O453" s="2"/>
       <c r="P453" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q453" t="s" s="2">
         <v>21</v>
@@ -53834,7 +53827,7 @@
         <v>21</v>
       </c>
       <c r="AG453" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH453" t="s" s="2">
         <v>76</v>
@@ -53854,10 +53847,10 @@
         <v>979</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
@@ -53957,10 +53950,10 @@
         <v>979</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -54062,10 +54055,10 @@
         <v>979</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -54169,10 +54162,10 @@
         <v>979</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -54217,7 +54210,7 @@
         <v>21</v>
       </c>
       <c r="T457" t="s" s="2">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="U457" t="s" s="2">
         <v>21</v>
@@ -54236,7 +54229,7 @@
       </c>
       <c r="Z457" s="2"/>
       <c r="AA457" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB457" t="s" s="2">
         <v>21</v>
@@ -54274,10 +54267,10 @@
         <v>979</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -54377,10 +54370,10 @@
         <v>979</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -54482,10 +54475,10 @@
         <v>979</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -54511,16 +54504,16 @@
         <v>165</v>
       </c>
       <c r="M460" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N460" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O460" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N460" t="s" s="2">
+      <c r="P460" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O460" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P460" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q460" t="s" s="2">
         <v>21</v>
@@ -54569,7 +54562,7 @@
         <v>21</v>
       </c>
       <c r="AG460" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH460" t="s" s="2">
         <v>76</v>
@@ -54589,10 +54582,10 @@
         <v>979</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -54692,10 +54685,10 @@
         <v>979</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
@@ -54797,10 +54790,10 @@
         <v>979</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -54904,10 +54897,10 @@
         <v>979</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -55009,10 +55002,10 @@
         <v>979</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -55114,10 +55107,10 @@
         <v>979</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -55219,10 +55212,10 @@
         <v>979</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
@@ -55326,10 +55319,10 @@
         <v>979</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -55355,16 +55348,16 @@
         <v>83</v>
       </c>
       <c r="M468" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N468" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O468" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N468" t="s" s="2">
+      <c r="P468" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O468" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P468" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q468" t="s" s="2">
         <v>21</v>
@@ -55413,7 +55406,7 @@
         <v>21</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>76</v>
@@ -55433,10 +55426,10 @@
         <v>979</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -55540,10 +55533,10 @@
         <v>979</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -55645,10 +55638,10 @@
         <v>979</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -55748,10 +55741,10 @@
         <v>979</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -55853,13 +55846,13 @@
         <v>979</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E473" t="s" s="2">
         <v>21</v>
@@ -55884,14 +55877,14 @@
         <v>222</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="N473" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="O473" s="2"/>
       <c r="P473" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="Q473" t="s" s="2">
         <v>21</v>
@@ -55940,7 +55933,7 @@
         <v>21</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -55960,10 +55953,10 @@
         <v>979</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -56063,10 +56056,10 @@
         <v>979</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -56168,10 +56161,10 @@
         <v>979</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -56216,7 +56209,7 @@
         <v>21</v>
       </c>
       <c r="T476" t="s" s="2">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="U476" t="s" s="2">
         <v>21</v>
@@ -56275,10 +56268,10 @@
         <v>979</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -56323,7 +56316,7 @@
         <v>21</v>
       </c>
       <c r="T477" t="s" s="2">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="U477" t="s" s="2">
         <v>21</v>
@@ -56342,7 +56335,7 @@
       </c>
       <c r="Z477" s="2"/>
       <c r="AA477" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AB477" t="s" s="2">
         <v>21</v>
@@ -56380,10 +56373,10 @@
         <v>979</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -56487,10 +56480,10 @@
         <v>979</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -56592,10 +56585,10 @@
         <v>979</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -56695,10 +56688,10 @@
         <v>979</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56800,10 +56793,10 @@
         <v>979</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -56829,23 +56822,23 @@
         <v>608</v>
       </c>
       <c r="M482" t="s" s="2">
+        <v>1222</v>
+      </c>
+      <c r="N482" t="s" s="2">
+        <v>1223</v>
+      </c>
+      <c r="O482" t="s" s="2">
         <v>1224</v>
       </c>
-      <c r="N482" t="s" s="2">
+      <c r="P482" t="s" s="2">
         <v>1225</v>
       </c>
-      <c r="O482" t="s" s="2">
+      <c r="Q482" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="R482" t="s" s="2">
         <v>1226</v>
       </c>
-      <c r="P482" t="s" s="2">
-        <v>1227</v>
-      </c>
-      <c r="Q482" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="R482" t="s" s="2">
-        <v>1228</v>
-      </c>
       <c r="S482" t="s" s="2">
         <v>21</v>
       </c>
@@ -56889,7 +56882,7 @@
         <v>21</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>76</v>
@@ -56909,10 +56902,10 @@
         <v>979</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -56935,19 +56928,19 @@
         <v>118</v>
       </c>
       <c r="L483" t="s" s="2">
+        <v>1228</v>
+      </c>
+      <c r="M483" t="s" s="2">
+        <v>1229</v>
+      </c>
+      <c r="N483" t="s" s="2">
         <v>1230</v>
       </c>
-      <c r="M483" t="s" s="2">
+      <c r="O483" t="s" s="2">
         <v>1231</v>
       </c>
-      <c r="N483" t="s" s="2">
+      <c r="P483" t="s" s="2">
         <v>1232</v>
-      </c>
-      <c r="O483" t="s" s="2">
-        <v>1233</v>
-      </c>
-      <c r="P483" t="s" s="2">
-        <v>1234</v>
       </c>
       <c r="Q483" t="s" s="2">
         <v>21</v>
@@ -56984,7 +56977,7 @@
         <v>21</v>
       </c>
       <c r="AC483" t="s" s="2">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="AD483" s="2"/>
       <c r="AE483" t="s" s="2">
@@ -56994,7 +56987,7 @@
         <v>92</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>76</v>
@@ -57014,13 +57007,13 @@
         <v>979</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D484" t="s" s="2">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E484" t="s" s="2">
         <v>21</v>
@@ -57042,19 +57035,19 @@
         <v>118</v>
       </c>
       <c r="L484" t="s" s="2">
+        <v>1236</v>
+      </c>
+      <c r="M484" t="s" s="2">
+        <v>1237</v>
+      </c>
+      <c r="N484" t="s" s="2">
         <v>1238</v>
       </c>
-      <c r="M484" t="s" s="2">
-        <v>1239</v>
-      </c>
-      <c r="N484" t="s" s="2">
-        <v>1240</v>
-      </c>
       <c r="O484" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="P484" t="s" s="2">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="Q484" t="s" s="2">
         <v>21</v>
@@ -57103,7 +57096,7 @@
         <v>21</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
@@ -57123,10 +57116,10 @@
         <v>979</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -57226,10 +57219,10 @@
         <v>979</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -57331,10 +57324,10 @@
         <v>979</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -57360,16 +57353,16 @@
         <v>187</v>
       </c>
       <c r="M487" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="N487" t="s" s="2">
+        <v>1246</v>
+      </c>
+      <c r="O487" t="s" s="2">
         <v>1247</v>
       </c>
-      <c r="N487" t="s" s="2">
+      <c r="P487" t="s" s="2">
         <v>1248</v>
-      </c>
-      <c r="O487" t="s" s="2">
-        <v>1249</v>
-      </c>
-      <c r="P487" t="s" s="2">
-        <v>1250</v>
       </c>
       <c r="Q487" t="s" s="2">
         <v>21</v>
@@ -57397,28 +57390,28 @@
         <v>233</v>
       </c>
       <c r="Z487" t="s" s="2">
+        <v>1249</v>
+      </c>
+      <c r="AA487" t="s" s="2">
+        <v>1250</v>
+      </c>
+      <c r="AB487" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC487" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD487" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE487" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF487" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AG487" t="s" s="2">
         <v>1251</v>
-      </c>
-      <c r="AA487" t="s" s="2">
-        <v>1252</v>
-      </c>
-      <c r="AB487" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC487" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD487" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE487" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF487" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AG487" t="s" s="2">
-        <v>1253</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
@@ -57438,10 +57431,10 @@
         <v>979</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -57467,16 +57460,16 @@
         <v>83</v>
       </c>
       <c r="M488" t="s" s="2">
+        <v>1254</v>
+      </c>
+      <c r="N488" t="s" s="2">
+        <v>1255</v>
+      </c>
+      <c r="O488" t="s" s="2">
         <v>1256</v>
       </c>
-      <c r="N488" t="s" s="2">
+      <c r="P488" t="s" s="2">
         <v>1257</v>
-      </c>
-      <c r="O488" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="P488" t="s" s="2">
-        <v>1259</v>
       </c>
       <c r="Q488" t="s" s="2">
         <v>21</v>
@@ -57525,7 +57518,7 @@
         <v>21</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
@@ -57545,14 +57538,14 @@
         <v>979</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F489" s="2"/>
       <c r="G489" t="s" s="2">
@@ -57574,13 +57567,13 @@
         <v>83</v>
       </c>
       <c r="M489" t="s" s="2">
+        <v>1262</v>
+      </c>
+      <c r="N489" t="s" s="2">
+        <v>1263</v>
+      </c>
+      <c r="O489" t="s" s="2">
         <v>1264</v>
-      </c>
-      <c r="N489" t="s" s="2">
-        <v>1265</v>
-      </c>
-      <c r="O489" t="s" s="2">
-        <v>1266</v>
       </c>
       <c r="P489" s="2"/>
       <c r="Q489" t="s" s="2">
@@ -57630,7 +57623,7 @@
         <v>21</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -57650,14 +57643,14 @@
         <v>979</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="F490" s="2"/>
       <c r="G490" t="s" s="2">
@@ -57679,13 +57672,13 @@
         <v>83</v>
       </c>
       <c r="M490" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="N490" t="s" s="2">
+        <v>1270</v>
+      </c>
+      <c r="O490" t="s" s="2">
         <v>1271</v>
-      </c>
-      <c r="N490" t="s" s="2">
-        <v>1272</v>
-      </c>
-      <c r="O490" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="P490" s="2"/>
       <c r="Q490" t="s" s="2">
@@ -57735,7 +57728,7 @@
         <v>21</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
@@ -57755,10 +57748,10 @@
         <v>979</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57784,10 +57777,10 @@
         <v>83</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="O491" s="2"/>
       <c r="P491" s="2"/>
@@ -57838,7 +57831,7 @@
         <v>21</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>76</v>
@@ -57858,10 +57851,10 @@
         <v>979</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57887,10 +57880,10 @@
         <v>83</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -57941,7 +57934,7 @@
         <v>21</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -57961,10 +57954,10 @@
         <v>979</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57990,14 +57983,14 @@
         <v>262</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="O493" s="2"/>
       <c r="P493" t="s" s="2">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="Q493" t="s" s="2">
         <v>21</v>
@@ -58046,7 +58039,7 @@
         <v>21</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -58066,13 +58059,13 @@
         <v>979</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D494" t="s" s="2">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="E494" t="s" s="2">
         <v>21</v>
@@ -58094,19 +58087,19 @@
         <v>118</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="O494" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="P494" t="s" s="2">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="Q494" t="s" s="2">
         <v>21</v>
@@ -58155,7 +58148,7 @@
         <v>21</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -58175,10 +58168,10 @@
         <v>979</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -58278,10 +58271,10 @@
         <v>979</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -58383,13 +58376,13 @@
         <v>979</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D497" t="s" s="2">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="E497" t="s" s="2">
         <v>21</v>
@@ -58411,13 +58404,13 @@
         <v>21</v>
       </c>
       <c r="L497" t="s" s="2">
+        <v>1297</v>
+      </c>
+      <c r="M497" t="s" s="2">
+        <v>1298</v>
+      </c>
+      <c r="N497" t="s" s="2">
         <v>1299</v>
-      </c>
-      <c r="M497" t="s" s="2">
-        <v>1300</v>
-      </c>
-      <c r="N497" t="s" s="2">
-        <v>1301</v>
       </c>
       <c r="O497" s="2"/>
       <c r="P497" s="2"/>
@@ -58488,10 +58481,10 @@
         <v>979</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -58517,16 +58510,16 @@
         <v>187</v>
       </c>
       <c r="M498" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="N498" t="s" s="2">
+        <v>1246</v>
+      </c>
+      <c r="O498" t="s" s="2">
         <v>1247</v>
       </c>
-      <c r="N498" t="s" s="2">
+      <c r="P498" t="s" s="2">
         <v>1248</v>
-      </c>
-      <c r="O498" t="s" s="2">
-        <v>1249</v>
-      </c>
-      <c r="P498" t="s" s="2">
-        <v>1250</v>
       </c>
       <c r="Q498" t="s" s="2">
         <v>21</v>
@@ -58536,7 +58529,7 @@
         <v>21</v>
       </c>
       <c r="T498" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="U498" t="s" s="2">
         <v>21</v>
@@ -58554,28 +58547,28 @@
         <v>233</v>
       </c>
       <c r="Z498" t="s" s="2">
+        <v>1249</v>
+      </c>
+      <c r="AA498" t="s" s="2">
+        <v>1250</v>
+      </c>
+      <c r="AB498" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC498" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD498" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE498" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF498" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AG498" t="s" s="2">
         <v>1251</v>
-      </c>
-      <c r="AA498" t="s" s="2">
-        <v>1252</v>
-      </c>
-      <c r="AB498" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC498" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD498" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE498" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF498" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AG498" t="s" s="2">
-        <v>1253</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -58595,10 +58588,10 @@
         <v>979</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -58624,16 +58617,16 @@
         <v>83</v>
       </c>
       <c r="M499" t="s" s="2">
+        <v>1254</v>
+      </c>
+      <c r="N499" t="s" s="2">
+        <v>1255</v>
+      </c>
+      <c r="O499" t="s" s="2">
         <v>1256</v>
       </c>
-      <c r="N499" t="s" s="2">
+      <c r="P499" t="s" s="2">
         <v>1257</v>
-      </c>
-      <c r="O499" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="P499" t="s" s="2">
-        <v>1259</v>
       </c>
       <c r="Q499" t="s" s="2">
         <v>21</v>
@@ -58682,7 +58675,7 @@
         <v>21</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>76</v>
@@ -58702,14 +58695,14 @@
         <v>979</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F500" s="2"/>
       <c r="G500" t="s" s="2">
@@ -58731,13 +58724,13 @@
         <v>83</v>
       </c>
       <c r="M500" t="s" s="2">
+        <v>1262</v>
+      </c>
+      <c r="N500" t="s" s="2">
+        <v>1263</v>
+      </c>
+      <c r="O500" t="s" s="2">
         <v>1264</v>
-      </c>
-      <c r="N500" t="s" s="2">
-        <v>1265</v>
-      </c>
-      <c r="O500" t="s" s="2">
-        <v>1266</v>
       </c>
       <c r="P500" s="2"/>
       <c r="Q500" t="s" s="2">
@@ -58787,7 +58780,7 @@
         <v>21</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>76</v>
@@ -58807,14 +58800,14 @@
         <v>979</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
@@ -58836,13 +58829,13 @@
         <v>83</v>
       </c>
       <c r="M501" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="N501" t="s" s="2">
+        <v>1270</v>
+      </c>
+      <c r="O501" t="s" s="2">
         <v>1271</v>
-      </c>
-      <c r="N501" t="s" s="2">
-        <v>1272</v>
-      </c>
-      <c r="O501" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="P501" s="2"/>
       <c r="Q501" t="s" s="2">
@@ -58892,7 +58885,7 @@
         <v>21</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>76</v>
@@ -58912,10 +58905,10 @@
         <v>979</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -58941,10 +58934,10 @@
         <v>83</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
@@ -58995,7 +58988,7 @@
         <v>21</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>76</v>
@@ -59015,10 +59008,10 @@
         <v>979</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -59044,10 +59037,10 @@
         <v>83</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
@@ -59098,7 +59091,7 @@
         <v>21</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
@@ -59118,10 +59111,10 @@
         <v>979</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -59147,14 +59140,14 @@
         <v>262</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="O504" s="2"/>
       <c r="P504" t="s" s="2">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="Q504" t="s" s="2">
         <v>21</v>
@@ -59203,7 +59196,7 @@
         <v>21</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
@@ -59223,10 +59216,10 @@
         <v>979</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -59249,19 +59242,19 @@
         <v>118</v>
       </c>
       <c r="L505" t="s" s="2">
+        <v>1308</v>
+      </c>
+      <c r="M505" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="N505" t="s" s="2">
         <v>1310</v>
       </c>
-      <c r="M505" t="s" s="2">
+      <c r="O505" t="s" s="2">
         <v>1311</v>
       </c>
-      <c r="N505" t="s" s="2">
+      <c r="P505" t="s" s="2">
         <v>1312</v>
-      </c>
-      <c r="O505" t="s" s="2">
-        <v>1313</v>
-      </c>
-      <c r="P505" t="s" s="2">
-        <v>1314</v>
       </c>
       <c r="Q505" t="s" s="2">
         <v>21</v>
@@ -59310,7 +59303,7 @@
         <v>21</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
@@ -59330,10 +59323,10 @@
         <v>979</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -59359,16 +59352,16 @@
         <v>187</v>
       </c>
       <c r="M506" t="s" s="2">
+        <v>1314</v>
+      </c>
+      <c r="N506" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="O506" t="s" s="2">
         <v>1316</v>
       </c>
-      <c r="N506" t="s" s="2">
+      <c r="P506" t="s" s="2">
         <v>1317</v>
-      </c>
-      <c r="O506" t="s" s="2">
-        <v>1318</v>
-      </c>
-      <c r="P506" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="Q506" t="s" s="2">
         <v>21</v>
@@ -59396,10 +59389,10 @@
         <v>233</v>
       </c>
       <c r="Z506" t="s" s="2">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="AA506" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="AB506" t="s" s="2">
         <v>21</v>
@@ -59417,7 +59410,7 @@
         <v>21</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -59437,10 +59430,10 @@
         <v>979</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59463,19 +59456,19 @@
         <v>118</v>
       </c>
       <c r="L507" t="s" s="2">
+        <v>1321</v>
+      </c>
+      <c r="M507" t="s" s="2">
+        <v>1322</v>
+      </c>
+      <c r="N507" t="s" s="2">
         <v>1323</v>
       </c>
-      <c r="M507" t="s" s="2">
+      <c r="O507" t="s" s="2">
         <v>1324</v>
       </c>
-      <c r="N507" t="s" s="2">
+      <c r="P507" t="s" s="2">
         <v>1325</v>
-      </c>
-      <c r="O507" t="s" s="2">
-        <v>1326</v>
-      </c>
-      <c r="P507" t="s" s="2">
-        <v>1327</v>
       </c>
       <c r="Q507" t="s" s="2">
         <v>21</v>
@@ -59524,7 +59517,7 @@
         <v>21</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -59544,10 +59537,10 @@
         <v>979</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -59570,19 +59563,19 @@
         <v>118</v>
       </c>
       <c r="L508" t="s" s="2">
+        <v>1327</v>
+      </c>
+      <c r="M508" t="s" s="2">
+        <v>1328</v>
+      </c>
+      <c r="N508" t="s" s="2">
         <v>1329</v>
       </c>
-      <c r="M508" t="s" s="2">
+      <c r="O508" t="s" s="2">
         <v>1330</v>
       </c>
-      <c r="N508" t="s" s="2">
+      <c r="P508" t="s" s="2">
         <v>1331</v>
-      </c>
-      <c r="O508" t="s" s="2">
-        <v>1332</v>
-      </c>
-      <c r="P508" t="s" s="2">
-        <v>1333</v>
       </c>
       <c r="Q508" t="s" s="2">
         <v>21</v>
@@ -59619,7 +59612,7 @@
         <v>21</v>
       </c>
       <c r="AC508" t="s" s="2">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="AD508" s="2"/>
       <c r="AE508" t="s" s="2">
@@ -59629,7 +59622,7 @@
         <v>92</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>76</v>
@@ -59649,13 +59642,13 @@
         <v>979</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="D509" t="s" s="2">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="E509" t="s" s="2">
         <v>21</v>
@@ -59680,16 +59673,16 @@
         <v>100</v>
       </c>
       <c r="M509" t="s" s="2">
+        <v>1328</v>
+      </c>
+      <c r="N509" t="s" s="2">
+        <v>1329</v>
+      </c>
+      <c r="O509" t="s" s="2">
         <v>1330</v>
       </c>
-      <c r="N509" t="s" s="2">
+      <c r="P509" t="s" s="2">
         <v>1331</v>
-      </c>
-      <c r="O509" t="s" s="2">
-        <v>1332</v>
-      </c>
-      <c r="P509" t="s" s="2">
-        <v>1333</v>
       </c>
       <c r="Q509" t="s" s="2">
         <v>21</v>
@@ -59738,7 +59731,7 @@
         <v>21</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>76</v>
@@ -59758,10 +59751,10 @@
         <v>979</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59787,16 +59780,16 @@
         <v>1043</v>
       </c>
       <c r="M510" t="s" s="2">
+        <v>1336</v>
+      </c>
+      <c r="N510" t="s" s="2">
+        <v>1337</v>
+      </c>
+      <c r="O510" t="s" s="2">
         <v>1338</v>
       </c>
-      <c r="N510" t="s" s="2">
+      <c r="P510" t="s" s="2">
         <v>1339</v>
-      </c>
-      <c r="O510" t="s" s="2">
-        <v>1340</v>
-      </c>
-      <c r="P510" t="s" s="2">
-        <v>1341</v>
       </c>
       <c r="Q510" t="s" s="2">
         <v>21</v>
@@ -59845,7 +59838,7 @@
         <v>21</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
@@ -59865,10 +59858,10 @@
         <v>979</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59894,14 +59887,14 @@
         <v>238</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="O511" s="2"/>
       <c r="P511" t="s" s="2">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="Q511" t="s" s="2">
         <v>21</v>
@@ -59930,7 +59923,7 @@
       </c>
       <c r="Z511" s="2"/>
       <c r="AA511" t="s" s="2">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="AB511" t="s" s="2">
         <v>21</v>
@@ -59948,7 +59941,7 @@
         <v>21</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
@@ -59968,10 +59961,10 @@
         <v>979</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59994,19 +59987,19 @@
         <v>21</v>
       </c>
       <c r="L512" t="s" s="2">
+        <v>1346</v>
+      </c>
+      <c r="M512" t="s" s="2">
+        <v>1347</v>
+      </c>
+      <c r="N512" t="s" s="2">
         <v>1348</v>
       </c>
-      <c r="M512" t="s" s="2">
+      <c r="O512" t="s" s="2">
         <v>1349</v>
       </c>
-      <c r="N512" t="s" s="2">
+      <c r="P512" t="s" s="2">
         <v>1350</v>
-      </c>
-      <c r="O512" t="s" s="2">
-        <v>1351</v>
-      </c>
-      <c r="P512" t="s" s="2">
-        <v>1352</v>
       </c>
       <c r="Q512" t="s" s="2">
         <v>21</v>
@@ -60055,7 +60048,7 @@
         <v>21</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -60075,10 +60068,10 @@
         <v>979</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -60101,19 +60094,19 @@
         <v>21</v>
       </c>
       <c r="L513" t="s" s="2">
+        <v>1352</v>
+      </c>
+      <c r="M513" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="N513" t="s" s="2">
         <v>1354</v>
       </c>
-      <c r="M513" t="s" s="2">
+      <c r="O513" t="s" s="2">
         <v>1355</v>
       </c>
-      <c r="N513" t="s" s="2">
+      <c r="P513" t="s" s="2">
         <v>1356</v>
-      </c>
-      <c r="O513" t="s" s="2">
-        <v>1357</v>
-      </c>
-      <c r="P513" t="s" s="2">
-        <v>1358</v>
       </c>
       <c r="Q513" t="s" s="2">
         <v>21</v>
@@ -60162,7 +60155,7 @@
         <v>21</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
@@ -60182,10 +60175,10 @@
         <v>979</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -60211,16 +60204,16 @@
         <v>351</v>
       </c>
       <c r="M514" t="s" s="2">
+        <v>1358</v>
+      </c>
+      <c r="N514" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="O514" t="s" s="2">
         <v>1360</v>
       </c>
-      <c r="N514" t="s" s="2">
+      <c r="P514" t="s" s="2">
         <v>1361</v>
-      </c>
-      <c r="O514" t="s" s="2">
-        <v>1362</v>
-      </c>
-      <c r="P514" t="s" s="2">
-        <v>1363</v>
       </c>
       <c r="Q514" t="s" s="2">
         <v>21</v>
@@ -60269,7 +60262,7 @@
         <v>21</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>76</v>
@@ -60281,7 +60274,7 @@
         <v>21</v>
       </c>
       <c r="AK514" t="s" s="2">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="515">
@@ -60289,10 +60282,10 @@
         <v>979</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -60392,10 +60385,10 @@
         <v>979</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -60493,13 +60486,13 @@
         <v>979</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C517" t="s" s="2">
+        <v>1364</v>
+      </c>
+      <c r="D517" t="s" s="2">
         <v>1366</v>
-      </c>
-      <c r="D517" t="s" s="2">
-        <v>1368</v>
       </c>
       <c r="E517" t="s" s="2">
         <v>21</v>
@@ -60521,13 +60514,13 @@
         <v>21</v>
       </c>
       <c r="L517" t="s" s="2">
+        <v>1367</v>
+      </c>
+      <c r="M517" t="s" s="2">
+        <v>1368</v>
+      </c>
+      <c r="N517" t="s" s="2">
         <v>1369</v>
-      </c>
-      <c r="M517" t="s" s="2">
-        <v>1370</v>
-      </c>
-      <c r="N517" t="s" s="2">
-        <v>1371</v>
       </c>
       <c r="O517" s="2"/>
       <c r="P517" s="2"/>
@@ -60598,13 +60591,13 @@
         <v>979</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D518" t="s" s="2">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="E518" t="s" s="2">
         <v>21</v>
@@ -60626,13 +60619,13 @@
         <v>21</v>
       </c>
       <c r="L518" t="s" s="2">
+        <v>1372</v>
+      </c>
+      <c r="M518" t="s" s="2">
+        <v>1373</v>
+      </c>
+      <c r="N518" t="s" s="2">
         <v>1374</v>
-      </c>
-      <c r="M518" t="s" s="2">
-        <v>1375</v>
-      </c>
-      <c r="N518" t="s" s="2">
-        <v>1376</v>
       </c>
       <c r="O518" s="2"/>
       <c r="P518" s="2"/>
@@ -60703,10 +60696,10 @@
         <v>979</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60810,10 +60803,10 @@
         <v>979</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60839,14 +60832,14 @@
         <v>238</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="Q520" t="s" s="2">
         <v>21</v>
@@ -60874,16 +60867,16 @@
         <v>169</v>
       </c>
       <c r="Z520" t="s" s="2">
+        <v>1380</v>
+      </c>
+      <c r="AA520" t="s" s="2">
+        <v>1381</v>
+      </c>
+      <c r="AB520" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC520" t="s" s="2">
         <v>1382</v>
-      </c>
-      <c r="AA520" t="s" s="2">
-        <v>1383</v>
-      </c>
-      <c r="AB520" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC520" t="s" s="2">
-        <v>1384</v>
       </c>
       <c r="AD520" s="2"/>
       <c r="AE520" t="s" s="2">
@@ -60893,7 +60886,7 @@
         <v>92</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
@@ -60913,13 +60906,13 @@
         <v>979</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D521" t="s" s="2">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="E521" t="s" s="2">
         <v>21</v>
@@ -60944,14 +60937,14 @@
         <v>238</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="Q521" t="s" s="2">
         <v>21</v>
@@ -60980,7 +60973,7 @@
       </c>
       <c r="Z521" s="2"/>
       <c r="AA521" t="s" s="2">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="AB521" t="s" s="2">
         <v>21</v>
@@ -60998,7 +60991,7 @@
         <v>21</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
@@ -61018,13 +61011,13 @@
         <v>979</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D522" t="s" s="2">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E522" t="s" s="2">
         <v>21</v>
@@ -61049,14 +61042,14 @@
         <v>238</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="O522" s="2"/>
       <c r="P522" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="Q522" t="s" s="2">
         <v>21</v>
@@ -61085,7 +61078,7 @@
       </c>
       <c r="Z522" s="2"/>
       <c r="AA522" t="s" s="2">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="AB522" t="s" s="2">
         <v>21</v>
@@ -61103,7 +61096,7 @@
         <v>21</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
@@ -61123,10 +61116,10 @@
         <v>979</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -61149,17 +61142,17 @@
         <v>21</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" t="s" s="2">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="Q523" t="s" s="2">
         <v>21</v>
@@ -61208,7 +61201,7 @@
         <v>21</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
@@ -61228,10 +61221,10 @@
         <v>979</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -61254,19 +61247,19 @@
         <v>21</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="M524" t="s" s="2">
+        <v>1396</v>
+      </c>
+      <c r="N524" t="s" s="2">
+        <v>1397</v>
+      </c>
+      <c r="O524" t="s" s="2">
         <v>1398</v>
       </c>
-      <c r="N524" t="s" s="2">
-        <v>1399</v>
-      </c>
-      <c r="O524" t="s" s="2">
-        <v>1400</v>
-      </c>
       <c r="P524" t="s" s="2">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="Q524" t="s" s="2">
         <v>21</v>
@@ -61315,7 +61308,7 @@
         <v>21</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -61335,10 +61328,10 @@
         <v>979</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -61361,17 +61354,17 @@
         <v>21</v>
       </c>
       <c r="L525" t="s" s="2">
+        <v>1400</v>
+      </c>
+      <c r="M525" t="s" s="2">
+        <v>1401</v>
+      </c>
+      <c r="N525" t="s" s="2">
         <v>1402</v>
-      </c>
-      <c r="M525" t="s" s="2">
-        <v>1403</v>
-      </c>
-      <c r="N525" t="s" s="2">
-        <v>1404</v>
       </c>
       <c r="O525" s="2"/>
       <c r="P525" t="s" s="2">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="Q525" t="s" s="2">
         <v>21</v>
@@ -61420,7 +61413,7 @@
         <v>21</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
@@ -61440,10 +61433,10 @@
         <v>979</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61469,14 +61462,14 @@
         <v>187</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="O526" s="2"/>
       <c r="P526" t="s" s="2">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="Q526" t="s" s="2">
         <v>21</v>
@@ -61504,10 +61497,10 @@
         <v>233</v>
       </c>
       <c r="Z526" t="s" s="2">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="AA526" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="AB526" t="s" s="2">
         <v>21</v>
@@ -61525,7 +61518,7 @@
         <v>21</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -61545,10 +61538,10 @@
         <v>979</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61574,14 +61567,14 @@
         <v>267</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" t="s" s="2">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="Q527" t="s" s="2">
         <v>21</v>
@@ -61630,7 +61623,7 @@
         <v>21</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -61639,7 +61632,7 @@
         <v>82</v>
       </c>
       <c r="AJ527" t="s" s="2">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="AK527" t="s" s="2">
         <v>103</v>
@@ -61650,10 +61643,10 @@
         <v>979</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61679,10 +61672,10 @@
         <v>262</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61733,7 +61726,7 @@
         <v>21</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61753,10 +61746,10 @@
         <v>979</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61782,16 +61775,16 @@
         <v>351</v>
       </c>
       <c r="M529" t="s" s="2">
+        <v>1416</v>
+      </c>
+      <c r="N529" t="s" s="2">
+        <v>1417</v>
+      </c>
+      <c r="O529" t="s" s="2">
         <v>1418</v>
       </c>
-      <c r="N529" t="s" s="2">
+      <c r="P529" t="s" s="2">
         <v>1419</v>
-      </c>
-      <c r="O529" t="s" s="2">
-        <v>1420</v>
-      </c>
-      <c r="P529" t="s" s="2">
-        <v>1421</v>
       </c>
       <c r="Q529" t="s" s="2">
         <v>21</v>
@@ -61840,7 +61833,7 @@
         <v>21</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -61860,10 +61853,10 @@
         <v>979</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61963,10 +61956,10 @@
         <v>979</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -62068,10 +62061,10 @@
         <v>979</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -62175,10 +62168,10 @@
         <v>979</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -62204,16 +62197,16 @@
         <v>238</v>
       </c>
       <c r="M533" t="s" s="2">
+        <v>1424</v>
+      </c>
+      <c r="N533" t="s" s="2">
+        <v>1425</v>
+      </c>
+      <c r="O533" t="s" s="2">
         <v>1426</v>
       </c>
-      <c r="N533" t="s" s="2">
+      <c r="P533" t="s" s="2">
         <v>1427</v>
-      </c>
-      <c r="O533" t="s" s="2">
-        <v>1428</v>
-      </c>
-      <c r="P533" t="s" s="2">
-        <v>1429</v>
       </c>
       <c r="Q533" t="s" s="2">
         <v>21</v>
@@ -62262,7 +62255,7 @@
         <v>21</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>82</v>
@@ -62282,10 +62275,10 @@
         <v>979</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -62311,16 +62304,16 @@
         <v>608</v>
       </c>
       <c r="M534" t="s" s="2">
+        <v>1429</v>
+      </c>
+      <c r="N534" t="s" s="2">
+        <v>1430</v>
+      </c>
+      <c r="O534" t="s" s="2">
         <v>1431</v>
       </c>
-      <c r="N534" t="s" s="2">
+      <c r="P534" t="s" s="2">
         <v>1432</v>
-      </c>
-      <c r="O534" t="s" s="2">
-        <v>1433</v>
-      </c>
-      <c r="P534" t="s" s="2">
-        <v>1434</v>
       </c>
       <c r="Q534" t="s" s="2">
         <v>21</v>
@@ -62369,7 +62362,7 @@
         <v>21</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>76</v>
@@ -62389,14 +62382,14 @@
         <v>979</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="F535" s="2"/>
       <c r="G535" t="s" s="2">
@@ -62415,16 +62408,16 @@
         <v>21</v>
       </c>
       <c r="L535" t="s" s="2">
+        <v>1435</v>
+      </c>
+      <c r="M535" t="s" s="2">
+        <v>1436</v>
+      </c>
+      <c r="N535" t="s" s="2">
         <v>1437</v>
       </c>
-      <c r="M535" t="s" s="2">
+      <c r="O535" t="s" s="2">
         <v>1438</v>
-      </c>
-      <c r="N535" t="s" s="2">
-        <v>1439</v>
-      </c>
-      <c r="O535" t="s" s="2">
-        <v>1440</v>
       </c>
       <c r="P535" s="2"/>
       <c r="Q535" t="s" s="2">
@@ -62474,7 +62467,7 @@
         <v>21</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
@@ -62494,10 +62487,10 @@
         <v>979</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62523,16 +62516,16 @@
         <v>561</v>
       </c>
       <c r="M536" t="s" s="2">
+        <v>1440</v>
+      </c>
+      <c r="N536" t="s" s="2">
+        <v>1441</v>
+      </c>
+      <c r="O536" t="s" s="2">
         <v>1442</v>
       </c>
-      <c r="N536" t="s" s="2">
+      <c r="P536" t="s" s="2">
         <v>1443</v>
-      </c>
-      <c r="O536" t="s" s="2">
-        <v>1444</v>
-      </c>
-      <c r="P536" t="s" s="2">
-        <v>1445</v>
       </c>
       <c r="Q536" t="s" s="2">
         <v>21</v>
@@ -62581,7 +62574,7 @@
         <v>21</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
@@ -62601,10 +62594,10 @@
         <v>979</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62630,16 +62623,16 @@
         <v>351</v>
       </c>
       <c r="M537" t="s" s="2">
+        <v>1445</v>
+      </c>
+      <c r="N537" t="s" s="2">
+        <v>1446</v>
+      </c>
+      <c r="O537" t="s" s="2">
         <v>1447</v>
       </c>
-      <c r="N537" t="s" s="2">
+      <c r="P537" t="s" s="2">
         <v>1448</v>
-      </c>
-      <c r="O537" t="s" s="2">
-        <v>1449</v>
-      </c>
-      <c r="P537" t="s" s="2">
-        <v>1450</v>
       </c>
       <c r="Q537" t="s" s="2">
         <v>21</v>
@@ -62688,7 +62681,7 @@
         <v>21</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62708,10 +62701,10 @@
         <v>979</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62811,10 +62804,10 @@
         <v>979</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62916,10 +62909,10 @@
         <v>979</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -63023,10 +63016,10 @@
         <v>979</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -63049,16 +63042,16 @@
         <v>118</v>
       </c>
       <c r="L541" t="s" s="2">
+        <v>1453</v>
+      </c>
+      <c r="M541" t="s" s="2">
+        <v>1454</v>
+      </c>
+      <c r="N541" t="s" s="2">
         <v>1455</v>
       </c>
-      <c r="M541" t="s" s="2">
+      <c r="O541" t="s" s="2">
         <v>1456</v>
-      </c>
-      <c r="N541" t="s" s="2">
-        <v>1457</v>
-      </c>
-      <c r="O541" t="s" s="2">
-        <v>1458</v>
       </c>
       <c r="P541" s="2"/>
       <c r="Q541" t="s" s="2">
@@ -63108,7 +63101,7 @@
         <v>21</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>82</v>
@@ -63128,10 +63121,10 @@
         <v>979</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -63157,10 +63150,10 @@
         <v>187</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="O542" s="2"/>
       <c r="P542" s="2"/>
@@ -63190,10 +63183,10 @@
         <v>233</v>
       </c>
       <c r="Z542" t="s" s="2">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="AA542" t="s" s="2">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="AB542" t="s" s="2">
         <v>21</v>
@@ -63211,7 +63204,7 @@
         <v>21</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>82</v>
@@ -63228,7 +63221,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>450</v>
@@ -63260,10 +63253,10 @@
         <v>78</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -63331,13 +63324,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -63436,13 +63429,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63539,13 +63532,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -63642,13 +63635,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63747,13 +63740,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63852,13 +63845,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63957,13 +63950,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -64062,13 +64055,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -64167,13 +64160,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="D552" t="s" s="2">
         <v>160</v>
@@ -64218,7 +64211,7 @@
         <v>21</v>
       </c>
       <c r="T552" t="s" s="2">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="U552" t="s" s="2">
         <v>21</v>
@@ -64274,13 +64267,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="D553" t="s" s="2">
         <v>163</v>
@@ -64325,7 +64318,7 @@
         <v>21</v>
       </c>
       <c r="T553" t="s" s="2">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="U553" t="s" s="2">
         <v>21</v>
@@ -64381,13 +64374,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -64486,13 +64479,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64591,13 +64584,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64696,13 +64689,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64801,13 +64794,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64906,13 +64899,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -65011,13 +65004,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -65112,16 +65105,16 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="C561" t="s" s="2">
+        <v>1487</v>
+      </c>
+      <c r="D561" t="s" s="2">
         <v>1489</v>
-      </c>
-      <c r="D561" t="s" s="2">
-        <v>1491</v>
       </c>
       <c r="E561" t="s" s="2">
         <v>21</v>
@@ -65143,13 +65136,13 @@
         <v>21</v>
       </c>
       <c r="L561" t="s" s="2">
+        <v>1490</v>
+      </c>
+      <c r="M561" t="s" s="2">
+        <v>1491</v>
+      </c>
+      <c r="N561" t="s" s="2">
         <v>1492</v>
-      </c>
-      <c r="M561" t="s" s="2">
-        <v>1493</v>
-      </c>
-      <c r="N561" t="s" s="2">
-        <v>1494</v>
       </c>
       <c r="O561" s="2"/>
       <c r="P561" s="2"/>
@@ -65217,13 +65210,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -65324,13 +65317,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -65356,14 +65349,14 @@
         <v>222</v>
       </c>
       <c r="M563" t="s" s="2">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="O563" s="2"/>
       <c r="P563" t="s" s="2">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="Q563" t="s" s="2">
         <v>21</v>
@@ -65400,10 +65393,10 @@
         <v>21</v>
       </c>
       <c r="AC563" t="s" s="2">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="AD563" t="s" s="2">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="AE563" t="s" s="2">
         <v>21</v>
@@ -65412,7 +65405,7 @@
         <v>92</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -65429,13 +65422,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -65532,13 +65525,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65637,13 +65630,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -65744,13 +65737,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -65814,7 +65807,7 @@
       </c>
       <c r="Z567" s="2"/>
       <c r="AA567" t="s" s="2">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="AB567" t="s" s="2">
         <v>21</v>
@@ -65849,13 +65842,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -65952,13 +65945,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -66057,13 +66050,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -66089,16 +66082,16 @@
         <v>165</v>
       </c>
       <c r="M570" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N570" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O570" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N570" t="s" s="2">
+      <c r="P570" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O570" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P570" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q570" t="s" s="2">
         <v>21</v>
@@ -66147,7 +66140,7 @@
         <v>21</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>76</v>
@@ -66164,13 +66157,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -66267,13 +66260,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -66372,13 +66365,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -66426,7 +66419,7 @@
         <v>21</v>
       </c>
       <c r="U573" t="s" s="2">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="V573" t="s" s="2">
         <v>21</v>
@@ -66479,13 +66472,13 @@
     </row>
     <row r="574">
       <c r="A574" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="D574" s="2"/>
       <c r="E574" t="s" s="2">
@@ -66584,13 +66577,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" t="s" s="2">
@@ -66689,13 +66682,13 @@
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" t="s" s="2">
@@ -66794,13 +66787,13 @@
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D577" s="2"/>
       <c r="E577" t="s" s="2">
@@ -66901,13 +66894,13 @@
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" t="s" s="2">
@@ -66933,16 +66926,16 @@
         <v>83</v>
       </c>
       <c r="M578" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N578" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O578" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N578" t="s" s="2">
+      <c r="P578" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O578" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P578" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q578" t="s" s="2">
         <v>21</v>
@@ -66991,7 +66984,7 @@
         <v>21</v>
       </c>
       <c r="AG578" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH578" t="s" s="2">
         <v>76</v>
@@ -67008,13 +67001,13 @@
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" t="s" s="2">
@@ -67043,7 +67036,7 @@
         <v>248</v>
       </c>
       <c r="N579" t="s" s="2">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="O579" t="s" s="2">
         <v>250</v>
@@ -67115,13 +67108,13 @@
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D580" s="2"/>
       <c r="E580" t="s" s="2">
@@ -67220,13 +67213,13 @@
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D581" s="2"/>
       <c r="E581" t="s" s="2">
@@ -67323,13 +67316,13 @@
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D582" s="2"/>
       <c r="E582" t="s" s="2">
@@ -67428,16 +67421,16 @@
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D583" t="s" s="2">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="E583" t="s" s="2">
         <v>21</v>
@@ -67462,14 +67455,14 @@
         <v>222</v>
       </c>
       <c r="M583" t="s" s="2">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="N583" t="s" s="2">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="O583" s="2"/>
       <c r="P583" t="s" s="2">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="Q583" t="s" s="2">
         <v>21</v>
@@ -67518,7 +67511,7 @@
         <v>21</v>
       </c>
       <c r="AG583" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="AH583" t="s" s="2">
         <v>76</v>
@@ -67535,13 +67528,13 @@
     </row>
     <row r="584">
       <c r="A584" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D584" s="2"/>
       <c r="E584" t="s" s="2">
@@ -67638,13 +67631,13 @@
     </row>
     <row r="585">
       <c r="A585" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" t="s" s="2">
@@ -67743,13 +67736,13 @@
     </row>
     <row r="586">
       <c r="A586" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D586" s="2"/>
       <c r="E586" t="s" s="2">
@@ -67850,13 +67843,13 @@
     </row>
     <row r="587">
       <c r="A587" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" t="s" s="2">
@@ -67882,7 +67875,7 @@
         <v>238</v>
       </c>
       <c r="M587" t="s" s="2">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="N587" t="s" s="2">
         <v>240</v>
@@ -67901,7 +67894,7 @@
         <v>21</v>
       </c>
       <c r="T587" t="s" s="2">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="U587" t="s" s="2">
         <v>21</v>
@@ -67920,7 +67913,7 @@
       </c>
       <c r="Z587" s="2"/>
       <c r="AA587" t="s" s="2">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="AB587" t="s" s="2">
         <v>21</v>
@@ -67955,13 +67948,13 @@
     </row>
     <row r="588">
       <c r="A588" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D588" s="2"/>
       <c r="E588" t="s" s="2">
@@ -68058,13 +68051,13 @@
     </row>
     <row r="589">
       <c r="A589" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" t="s" s="2">
@@ -68163,13 +68156,13 @@
     </row>
     <row r="590">
       <c r="A590" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D590" s="2"/>
       <c r="E590" t="s" s="2">
@@ -68195,16 +68188,16 @@
         <v>165</v>
       </c>
       <c r="M590" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N590" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O590" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N590" t="s" s="2">
+      <c r="P590" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O590" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P590" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q590" t="s" s="2">
         <v>21</v>
@@ -68253,7 +68246,7 @@
         <v>21</v>
       </c>
       <c r="AG590" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH590" t="s" s="2">
         <v>76</v>
@@ -68270,13 +68263,13 @@
     </row>
     <row r="591">
       <c r="A591" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D591" s="2"/>
       <c r="E591" t="s" s="2">
@@ -68373,13 +68366,13 @@
     </row>
     <row r="592">
       <c r="A592" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D592" s="2"/>
       <c r="E592" t="s" s="2">
@@ -68478,13 +68471,13 @@
     </row>
     <row r="593">
       <c r="A593" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" t="s" s="2">
@@ -68532,7 +68525,7 @@
         <v>21</v>
       </c>
       <c r="U593" t="s" s="2">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="V593" t="s" s="2">
         <v>21</v>
@@ -68585,13 +68578,13 @@
     </row>
     <row r="594">
       <c r="A594" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="C594" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="D594" s="2"/>
       <c r="E594" t="s" s="2">
@@ -68690,13 +68683,13 @@
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="C595" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D595" s="2"/>
       <c r="E595" t="s" s="2">
@@ -68795,13 +68788,13 @@
     </row>
     <row r="596">
       <c r="A596" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="C596" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D596" s="2"/>
       <c r="E596" t="s" s="2">
@@ -68900,13 +68893,13 @@
     </row>
     <row r="597">
       <c r="A597" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C597" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D597" s="2"/>
       <c r="E597" t="s" s="2">
@@ -69007,13 +69000,13 @@
     </row>
     <row r="598">
       <c r="A598" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C598" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="D598" s="2"/>
       <c r="E598" t="s" s="2">
@@ -69039,16 +69032,16 @@
         <v>83</v>
       </c>
       <c r="M598" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N598" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O598" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N598" t="s" s="2">
+      <c r="P598" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O598" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P598" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q598" t="s" s="2">
         <v>21</v>
@@ -69097,7 +69090,7 @@
         <v>21</v>
       </c>
       <c r="AG598" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH598" t="s" s="2">
         <v>76</v>
@@ -69114,13 +69107,13 @@
     </row>
     <row r="599">
       <c r="A599" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="C599" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D599" s="2"/>
       <c r="E599" t="s" s="2">
@@ -69149,7 +69142,7 @@
         <v>248</v>
       </c>
       <c r="N599" t="s" s="2">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="O599" t="s" s="2">
         <v>250</v>
@@ -69221,13 +69214,13 @@
     </row>
     <row r="600">
       <c r="A600" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B600" t="s" s="2">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="C600" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D600" s="2"/>
       <c r="E600" t="s" s="2">
@@ -69253,7 +69246,7 @@
         <v>83</v>
       </c>
       <c r="M600" t="s" s="2">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="N600" t="s" s="2">
         <v>257</v>
@@ -69326,13 +69319,13 @@
     </row>
     <row r="601">
       <c r="A601" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C601" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D601" s="2"/>
       <c r="E601" t="s" s="2">
@@ -69429,13 +69422,13 @@
     </row>
     <row r="602">
       <c r="A602" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B602" t="s" s="2">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="C602" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D602" s="2"/>
       <c r="E602" t="s" s="2">
@@ -69534,16 +69527,16 @@
     </row>
     <row r="603">
       <c r="A603" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B603" t="s" s="2">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="C603" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D603" t="s" s="2">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="E603" t="s" s="2">
         <v>21</v>
@@ -69568,14 +69561,14 @@
         <v>222</v>
       </c>
       <c r="M603" t="s" s="2">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="N603" t="s" s="2">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="O603" s="2"/>
       <c r="P603" t="s" s="2">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="Q603" t="s" s="2">
         <v>21</v>
@@ -69624,7 +69617,7 @@
         <v>21</v>
       </c>
       <c r="AG603" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="AH603" t="s" s="2">
         <v>76</v>
@@ -69641,13 +69634,13 @@
     </row>
     <row r="604">
       <c r="A604" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B604" t="s" s="2">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="C604" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D604" s="2"/>
       <c r="E604" t="s" s="2">
@@ -69744,13 +69737,13 @@
     </row>
     <row r="605">
       <c r="A605" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B605" t="s" s="2">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="C605" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D605" s="2"/>
       <c r="E605" t="s" s="2">
@@ -69849,13 +69842,13 @@
     </row>
     <row r="606">
       <c r="A606" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B606" t="s" s="2">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="C606" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D606" s="2"/>
       <c r="E606" t="s" s="2">
@@ -69956,13 +69949,13 @@
     </row>
     <row r="607">
       <c r="A607" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B607" t="s" s="2">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="C607" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D607" s="2"/>
       <c r="E607" t="s" s="2">
@@ -69988,7 +69981,7 @@
         <v>238</v>
       </c>
       <c r="M607" t="s" s="2">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="N607" t="s" s="2">
         <v>240</v>
@@ -70007,7 +70000,7 @@
         <v>21</v>
       </c>
       <c r="T607" t="s" s="2">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="U607" t="s" s="2">
         <v>21</v>
@@ -70026,7 +70019,7 @@
       </c>
       <c r="Z607" s="2"/>
       <c r="AA607" t="s" s="2">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="AB607" t="s" s="2">
         <v>21</v>
@@ -70061,13 +70054,13 @@
     </row>
     <row r="608">
       <c r="A608" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B608" t="s" s="2">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="C608" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D608" s="2"/>
       <c r="E608" t="s" s="2">
@@ -70164,13 +70157,13 @@
     </row>
     <row r="609">
       <c r="A609" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B609" t="s" s="2">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C609" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D609" s="2"/>
       <c r="E609" t="s" s="2">
@@ -70269,13 +70262,13 @@
     </row>
     <row r="610">
       <c r="A610" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B610" t="s" s="2">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="C610" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D610" s="2"/>
       <c r="E610" t="s" s="2">
@@ -70301,16 +70294,16 @@
         <v>165</v>
       </c>
       <c r="M610" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N610" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O610" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N610" t="s" s="2">
+      <c r="P610" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O610" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P610" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q610" t="s" s="2">
         <v>21</v>
@@ -70359,7 +70352,7 @@
         <v>21</v>
       </c>
       <c r="AG610" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH610" t="s" s="2">
         <v>76</v>
@@ -70376,13 +70369,13 @@
     </row>
     <row r="611">
       <c r="A611" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B611" t="s" s="2">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="C611" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D611" s="2"/>
       <c r="E611" t="s" s="2">
@@ -70479,13 +70472,13 @@
     </row>
     <row r="612">
       <c r="A612" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B612" t="s" s="2">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="C612" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D612" s="2"/>
       <c r="E612" t="s" s="2">
@@ -70584,13 +70577,13 @@
     </row>
     <row r="613">
       <c r="A613" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B613" t="s" s="2">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C613" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="D613" s="2"/>
       <c r="E613" t="s" s="2">
@@ -70638,7 +70631,7 @@
         <v>21</v>
       </c>
       <c r="U613" t="s" s="2">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="V613" t="s" s="2">
         <v>21</v>
@@ -70691,13 +70684,13 @@
     </row>
     <row r="614">
       <c r="A614" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B614" t="s" s="2">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="C614" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="D614" s="2"/>
       <c r="E614" t="s" s="2">
@@ -70796,13 +70789,13 @@
     </row>
     <row r="615">
       <c r="A615" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B615" t="s" s="2">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="C615" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D615" s="2"/>
       <c r="E615" t="s" s="2">
@@ -70901,13 +70894,13 @@
     </row>
     <row r="616">
       <c r="A616" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B616" t="s" s="2">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="C616" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D616" s="2"/>
       <c r="E616" t="s" s="2">
@@ -71006,13 +70999,13 @@
     </row>
     <row r="617">
       <c r="A617" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B617" t="s" s="2">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="C617" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D617" s="2"/>
       <c r="E617" t="s" s="2">
@@ -71113,13 +71106,13 @@
     </row>
     <row r="618">
       <c r="A618" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B618" t="s" s="2">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="C618" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="D618" s="2"/>
       <c r="E618" t="s" s="2">
@@ -71145,16 +71138,16 @@
         <v>83</v>
       </c>
       <c r="M618" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N618" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O618" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N618" t="s" s="2">
+      <c r="P618" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O618" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P618" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q618" t="s" s="2">
         <v>21</v>
@@ -71203,7 +71196,7 @@
         <v>21</v>
       </c>
       <c r="AG618" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH618" t="s" s="2">
         <v>76</v>
@@ -71220,13 +71213,13 @@
     </row>
     <row r="619">
       <c r="A619" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B619" t="s" s="2">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="C619" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D619" s="2"/>
       <c r="E619" t="s" s="2">
@@ -71255,7 +71248,7 @@
         <v>248</v>
       </c>
       <c r="N619" t="s" s="2">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="O619" t="s" s="2">
         <v>250</v>
@@ -71271,7 +71264,7 @@
         <v>21</v>
       </c>
       <c r="T619" t="s" s="2">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="U619" t="s" s="2">
         <v>253</v>
@@ -71327,13 +71320,13 @@
     </row>
     <row r="620">
       <c r="A620" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B620" t="s" s="2">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="C620" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D620" s="2"/>
       <c r="E620" t="s" s="2">
@@ -71359,7 +71352,7 @@
         <v>83</v>
       </c>
       <c r="M620" t="s" s="2">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="N620" t="s" s="2">
         <v>257</v>
@@ -71432,13 +71425,13 @@
     </row>
     <row r="621">
       <c r="A621" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B621" t="s" s="2">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="C621" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D621" s="2"/>
       <c r="E621" t="s" s="2">
@@ -71535,13 +71528,13 @@
     </row>
     <row r="622">
       <c r="A622" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B622" t="s" s="2">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="C622" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D622" s="2"/>
       <c r="E622" t="s" s="2">
@@ -71640,16 +71633,16 @@
     </row>
     <row r="623">
       <c r="A623" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B623" t="s" s="2">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="C623" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D623" t="s" s="2">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E623" t="s" s="2">
         <v>21</v>
@@ -71674,14 +71667,14 @@
         <v>222</v>
       </c>
       <c r="M623" t="s" s="2">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="N623" t="s" s="2">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="O623" s="2"/>
       <c r="P623" t="s" s="2">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="Q623" t="s" s="2">
         <v>21</v>
@@ -71730,7 +71723,7 @@
         <v>21</v>
       </c>
       <c r="AG623" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="AH623" t="s" s="2">
         <v>76</v>
@@ -71747,13 +71740,13 @@
     </row>
     <row r="624">
       <c r="A624" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B624" t="s" s="2">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="C624" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D624" s="2"/>
       <c r="E624" t="s" s="2">
@@ -71850,13 +71843,13 @@
     </row>
     <row r="625">
       <c r="A625" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B625" t="s" s="2">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="C625" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D625" s="2"/>
       <c r="E625" t="s" s="2">
@@ -71955,13 +71948,13 @@
     </row>
     <row r="626">
       <c r="A626" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B626" t="s" s="2">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="C626" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D626" s="2"/>
       <c r="E626" t="s" s="2">
@@ -72062,13 +72055,13 @@
     </row>
     <row r="627">
       <c r="A627" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B627" t="s" s="2">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="C627" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D627" s="2"/>
       <c r="E627" t="s" s="2">
@@ -72113,7 +72106,7 @@
         <v>21</v>
       </c>
       <c r="T627" t="s" s="2">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="U627" t="s" s="2">
         <v>21</v>
@@ -72132,7 +72125,7 @@
       </c>
       <c r="Z627" s="2"/>
       <c r="AA627" t="s" s="2">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="AB627" t="s" s="2">
         <v>21</v>
@@ -72167,13 +72160,13 @@
     </row>
     <row r="628">
       <c r="A628" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B628" t="s" s="2">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="C628" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D628" s="2"/>
       <c r="E628" t="s" s="2">
@@ -72270,13 +72263,13 @@
     </row>
     <row r="629">
       <c r="A629" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B629" t="s" s="2">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="C629" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D629" s="2"/>
       <c r="E629" t="s" s="2">
@@ -72375,13 +72368,13 @@
     </row>
     <row r="630">
       <c r="A630" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B630" t="s" s="2">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="C630" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D630" s="2"/>
       <c r="E630" t="s" s="2">
@@ -72407,16 +72400,16 @@
         <v>165</v>
       </c>
       <c r="M630" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N630" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O630" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N630" t="s" s="2">
+      <c r="P630" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O630" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P630" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q630" t="s" s="2">
         <v>21</v>
@@ -72465,7 +72458,7 @@
         <v>21</v>
       </c>
       <c r="AG630" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH630" t="s" s="2">
         <v>76</v>
@@ -72482,13 +72475,13 @@
     </row>
     <row r="631">
       <c r="A631" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B631" t="s" s="2">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="C631" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D631" s="2"/>
       <c r="E631" t="s" s="2">
@@ -72585,13 +72578,13 @@
     </row>
     <row r="632">
       <c r="A632" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B632" t="s" s="2">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="C632" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D632" s="2"/>
       <c r="E632" t="s" s="2">
@@ -72690,13 +72683,13 @@
     </row>
     <row r="633">
       <c r="A633" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B633" t="s" s="2">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="C633" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="D633" s="2"/>
       <c r="E633" t="s" s="2">
@@ -72744,7 +72737,7 @@
         <v>21</v>
       </c>
       <c r="U633" t="s" s="2">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="V633" t="s" s="2">
         <v>21</v>
@@ -72797,13 +72790,13 @@
     </row>
     <row r="634">
       <c r="A634" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B634" t="s" s="2">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="C634" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="D634" s="2"/>
       <c r="E634" t="s" s="2">
@@ -72902,13 +72895,13 @@
     </row>
     <row r="635">
       <c r="A635" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B635" t="s" s="2">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="C635" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D635" s="2"/>
       <c r="E635" t="s" s="2">
@@ -73007,13 +73000,13 @@
     </row>
     <row r="636">
       <c r="A636" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B636" t="s" s="2">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="C636" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D636" s="2"/>
       <c r="E636" t="s" s="2">
@@ -73112,13 +73105,13 @@
     </row>
     <row r="637">
       <c r="A637" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B637" t="s" s="2">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="C637" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D637" s="2"/>
       <c r="E637" t="s" s="2">
@@ -73219,13 +73212,13 @@
     </row>
     <row r="638">
       <c r="A638" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B638" t="s" s="2">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="C638" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="D638" s="2"/>
       <c r="E638" t="s" s="2">
@@ -73251,16 +73244,16 @@
         <v>83</v>
       </c>
       <c r="M638" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N638" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O638" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N638" t="s" s="2">
+      <c r="P638" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O638" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P638" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q638" t="s" s="2">
         <v>21</v>
@@ -73309,7 +73302,7 @@
         <v>21</v>
       </c>
       <c r="AG638" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH638" t="s" s="2">
         <v>76</v>
@@ -73326,13 +73319,13 @@
     </row>
     <row r="639">
       <c r="A639" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B639" t="s" s="2">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="C639" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D639" s="2"/>
       <c r="E639" t="s" s="2">
@@ -73361,7 +73354,7 @@
         <v>248</v>
       </c>
       <c r="N639" t="s" s="2">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="O639" t="s" s="2">
         <v>250</v>
@@ -73377,7 +73370,7 @@
         <v>21</v>
       </c>
       <c r="T639" t="s" s="2">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="U639" t="s" s="2">
         <v>253</v>
@@ -73433,13 +73426,13 @@
     </row>
     <row r="640">
       <c r="A640" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B640" t="s" s="2">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="C640" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D640" s="2"/>
       <c r="E640" t="s" s="2">
@@ -73538,13 +73531,13 @@
     </row>
     <row r="641">
       <c r="A641" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B641" t="s" s="2">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="C641" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D641" s="2"/>
       <c r="E641" t="s" s="2">
@@ -73641,13 +73634,13 @@
     </row>
     <row r="642">
       <c r="A642" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B642" t="s" s="2">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="C642" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D642" s="2"/>
       <c r="E642" t="s" s="2">
@@ -73746,16 +73739,16 @@
     </row>
     <row r="643">
       <c r="A643" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B643" t="s" s="2">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="C643" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D643" t="s" s="2">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="E643" t="s" s="2">
         <v>21</v>
@@ -73780,14 +73773,14 @@
         <v>222</v>
       </c>
       <c r="M643" t="s" s="2">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="N643" t="s" s="2">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="O643" s="2"/>
       <c r="P643" t="s" s="2">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="Q643" t="s" s="2">
         <v>21</v>
@@ -73836,7 +73829,7 @@
         <v>21</v>
       </c>
       <c r="AG643" t="s" s="2">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="AH643" t="s" s="2">
         <v>76</v>
@@ -73853,13 +73846,13 @@
     </row>
     <row r="644">
       <c r="A644" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B644" t="s" s="2">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C644" t="s" s="2">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D644" s="2"/>
       <c r="E644" t="s" s="2">
@@ -73956,13 +73949,13 @@
     </row>
     <row r="645">
       <c r="A645" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B645" t="s" s="2">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="C645" t="s" s="2">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D645" s="2"/>
       <c r="E645" t="s" s="2">
@@ -74061,13 +74054,13 @@
     </row>
     <row r="646">
       <c r="A646" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B646" t="s" s="2">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="C646" t="s" s="2">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D646" s="2"/>
       <c r="E646" t="s" s="2">
@@ -74168,13 +74161,13 @@
     </row>
     <row r="647">
       <c r="A647" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B647" t="s" s="2">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="C647" t="s" s="2">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D647" s="2"/>
       <c r="E647" t="s" s="2">
@@ -74219,7 +74212,7 @@
         <v>21</v>
       </c>
       <c r="T647" t="s" s="2">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="U647" t="s" s="2">
         <v>21</v>
@@ -74238,7 +74231,7 @@
       </c>
       <c r="Z647" s="2"/>
       <c r="AA647" t="s" s="2">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="AB647" t="s" s="2">
         <v>21</v>
@@ -74273,13 +74266,13 @@
     </row>
     <row r="648">
       <c r="A648" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B648" t="s" s="2">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="C648" t="s" s="2">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D648" s="2"/>
       <c r="E648" t="s" s="2">
@@ -74376,13 +74369,13 @@
     </row>
     <row r="649">
       <c r="A649" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B649" t="s" s="2">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="C649" t="s" s="2">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D649" s="2"/>
       <c r="E649" t="s" s="2">
@@ -74481,13 +74474,13 @@
     </row>
     <row r="650">
       <c r="A650" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B650" t="s" s="2">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="C650" t="s" s="2">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D650" s="2"/>
       <c r="E650" t="s" s="2">
@@ -74513,16 +74506,16 @@
         <v>165</v>
       </c>
       <c r="M650" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N650" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O650" t="s" s="2">
         <v>1077</v>
       </c>
-      <c r="N650" t="s" s="2">
+      <c r="P650" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="O650" t="s" s="2">
-        <v>1079</v>
-      </c>
-      <c r="P650" t="s" s="2">
-        <v>1080</v>
       </c>
       <c r="Q650" t="s" s="2">
         <v>21</v>
@@ -74571,7 +74564,7 @@
         <v>21</v>
       </c>
       <c r="AG650" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AH650" t="s" s="2">
         <v>76</v>
@@ -74588,13 +74581,13 @@
     </row>
     <row r="651">
       <c r="A651" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B651" t="s" s="2">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="C651" t="s" s="2">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D651" s="2"/>
       <c r="E651" t="s" s="2">
@@ -74691,13 +74684,13 @@
     </row>
     <row r="652">
       <c r="A652" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B652" t="s" s="2">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="C652" t="s" s="2">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D652" s="2"/>
       <c r="E652" t="s" s="2">
@@ -74796,13 +74789,13 @@
     </row>
     <row r="653">
       <c r="A653" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B653" t="s" s="2">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="C653" t="s" s="2">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="D653" s="2"/>
       <c r="E653" t="s" s="2">
@@ -74850,7 +74843,7 @@
         <v>21</v>
       </c>
       <c r="U653" t="s" s="2">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="V653" t="s" s="2">
         <v>21</v>
@@ -74903,13 +74896,13 @@
     </row>
     <row r="654">
       <c r="A654" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B654" t="s" s="2">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="C654" t="s" s="2">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="D654" s="2"/>
       <c r="E654" t="s" s="2">
@@ -75008,13 +75001,13 @@
     </row>
     <row r="655">
       <c r="A655" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B655" t="s" s="2">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="C655" t="s" s="2">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D655" s="2"/>
       <c r="E655" t="s" s="2">
@@ -75113,13 +75106,13 @@
     </row>
     <row r="656">
       <c r="A656" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B656" t="s" s="2">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="C656" t="s" s="2">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D656" s="2"/>
       <c r="E656" t="s" s="2">
@@ -75218,13 +75211,13 @@
     </row>
     <row r="657">
       <c r="A657" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B657" t="s" s="2">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="C657" t="s" s="2">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D657" s="2"/>
       <c r="E657" t="s" s="2">
@@ -75325,13 +75318,13 @@
     </row>
     <row r="658">
       <c r="A658" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B658" t="s" s="2">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="C658" t="s" s="2">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="D658" s="2"/>
       <c r="E658" t="s" s="2">
@@ -75357,16 +75350,16 @@
         <v>83</v>
       </c>
       <c r="M658" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N658" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O658" t="s" s="2">
         <v>1098</v>
       </c>
-      <c r="N658" t="s" s="2">
+      <c r="P658" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="O658" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="P658" t="s" s="2">
-        <v>1101</v>
       </c>
       <c r="Q658" t="s" s="2">
         <v>21</v>
@@ -75415,7 +75408,7 @@
         <v>21</v>
       </c>
       <c r="AG658" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AH658" t="s" s="2">
         <v>76</v>
@@ -75432,13 +75425,13 @@
     </row>
     <row r="659">
       <c r="A659" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B659" t="s" s="2">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="C659" t="s" s="2">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D659" s="2"/>
       <c r="E659" t="s" s="2">
@@ -75467,7 +75460,7 @@
         <v>248</v>
       </c>
       <c r="N659" t="s" s="2">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="O659" t="s" s="2">
         <v>250</v>
@@ -75483,7 +75476,7 @@
         <v>21</v>
       </c>
       <c r="T659" t="s" s="2">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="U659" t="s" s="2">
         <v>253</v>
@@ -75539,13 +75532,13 @@
     </row>
     <row r="660">
       <c r="A660" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B660" t="s" s="2">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="C660" t="s" s="2">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D660" s="2"/>
       <c r="E660" t="s" s="2">
@@ -75644,13 +75637,13 @@
     </row>
     <row r="661">
       <c r="A661" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B661" t="s" s="2">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D661" s="2"/>
       <c r="E661" t="s" s="2">
@@ -75747,13 +75740,13 @@
     </row>
     <row r="662">
       <c r="A662" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="C662" t="s" s="2">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D662" s="2"/>
       <c r="E662" t="s" s="2">
@@ -75852,13 +75845,13 @@
     </row>
     <row r="663">
       <c r="A663" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="C663" t="s" s="2">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D663" s="2"/>
       <c r="E663" t="s" s="2">
@@ -75884,22 +75877,22 @@
         <v>608</v>
       </c>
       <c r="M663" t="s" s="2">
+        <v>1622</v>
+      </c>
+      <c r="N663" t="s" s="2">
+        <v>1623</v>
+      </c>
+      <c r="O663" t="s" s="2">
         <v>1624</v>
       </c>
-      <c r="N663" t="s" s="2">
+      <c r="P663" t="s" s="2">
         <v>1625</v>
       </c>
-      <c r="O663" t="s" s="2">
-        <v>1626</v>
-      </c>
-      <c r="P663" t="s" s="2">
-        <v>1627</v>
-      </c>
       <c r="Q663" t="s" s="2">
         <v>21</v>
       </c>
       <c r="R663" t="s" s="2">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="S663" t="s" s="2">
         <v>21</v>
@@ -75944,7 +75937,7 @@
         <v>21</v>
       </c>
       <c r="AG663" t="s" s="2">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="AH663" t="s" s="2">
         <v>76</v>
@@ -75961,13 +75954,13 @@
     </row>
     <row r="664">
       <c r="A664" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="C664" t="s" s="2">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D664" s="2"/>
       <c r="E664" t="s" s="2">
@@ -75990,19 +75983,19 @@
         <v>118</v>
       </c>
       <c r="L664" t="s" s="2">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="M664" t="s" s="2">
+        <v>1627</v>
+      </c>
+      <c r="N664" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="O664" t="s" s="2">
         <v>1629</v>
       </c>
-      <c r="N664" t="s" s="2">
+      <c r="P664" t="s" s="2">
         <v>1630</v>
-      </c>
-      <c r="O664" t="s" s="2">
-        <v>1631</v>
-      </c>
-      <c r="P664" t="s" s="2">
-        <v>1632</v>
       </c>
       <c r="Q664" t="s" s="2">
         <v>21</v>
@@ -76051,7 +76044,7 @@
         <v>21</v>
       </c>
       <c r="AG664" t="s" s="2">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="AH664" t="s" s="2">
         <v>76</v>
@@ -76068,13 +76061,13 @@
     </row>
     <row r="665">
       <c r="A665" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="C665" t="s" s="2">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="D665" s="2"/>
       <c r="E665" t="s" s="2">
@@ -76097,19 +76090,19 @@
         <v>118</v>
       </c>
       <c r="L665" t="s" s="2">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="M665" t="s" s="2">
+        <v>1632</v>
+      </c>
+      <c r="N665" t="s" s="2">
+        <v>1633</v>
+      </c>
+      <c r="O665" t="s" s="2">
         <v>1634</v>
       </c>
-      <c r="N665" t="s" s="2">
+      <c r="P665" t="s" s="2">
         <v>1635</v>
-      </c>
-      <c r="O665" t="s" s="2">
-        <v>1636</v>
-      </c>
-      <c r="P665" t="s" s="2">
-        <v>1637</v>
       </c>
       <c r="Q665" t="s" s="2">
         <v>21</v>
@@ -76158,7 +76151,7 @@
         <v>21</v>
       </c>
       <c r="AG665" t="s" s="2">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="AH665" t="s" s="2">
         <v>76</v>
@@ -76175,13 +76168,13 @@
     </row>
     <row r="666">
       <c r="A666" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="C666" t="s" s="2">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="D666" s="2"/>
       <c r="E666" t="s" s="2">
@@ -76207,16 +76200,16 @@
         <v>1043</v>
       </c>
       <c r="M666" t="s" s="2">
+        <v>1637</v>
+      </c>
+      <c r="N666" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="O666" t="s" s="2">
         <v>1639</v>
       </c>
-      <c r="N666" t="s" s="2">
+      <c r="P666" t="s" s="2">
         <v>1640</v>
-      </c>
-      <c r="O666" t="s" s="2">
-        <v>1641</v>
-      </c>
-      <c r="P666" t="s" s="2">
-        <v>1642</v>
       </c>
       <c r="Q666" t="s" s="2">
         <v>21</v>
@@ -76265,7 +76258,7 @@
         <v>21</v>
       </c>
       <c r="AG666" t="s" s="2">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="AH666" t="s" s="2">
         <v>76</v>
@@ -76282,13 +76275,13 @@
     </row>
     <row r="667">
       <c r="A667" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="C667" t="s" s="2">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="D667" s="2"/>
       <c r="E667" t="s" s="2">
@@ -76314,14 +76307,14 @@
         <v>187</v>
       </c>
       <c r="M667" t="s" s="2">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="N667" t="s" s="2">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="O667" s="2"/>
       <c r="P667" t="s" s="2">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="Q667" t="s" s="2">
         <v>21</v>
@@ -76349,10 +76342,10 @@
         <v>233</v>
       </c>
       <c r="Z667" t="s" s="2">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="AA667" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="AB667" t="s" s="2">
         <v>21</v>
@@ -76370,7 +76363,7 @@
         <v>21</v>
       </c>
       <c r="AG667" t="s" s="2">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="AH667" t="s" s="2">
         <v>76</v>
@@ -76387,13 +76380,13 @@
     </row>
     <row r="668">
       <c r="A668" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B668" t="s" s="2">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="C668" t="s" s="2">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="D668" s="2"/>
       <c r="E668" t="s" s="2">
@@ -76416,17 +76409,17 @@
         <v>118</v>
       </c>
       <c r="L668" t="s" s="2">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="M668" t="s" s="2">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="N668" t="s" s="2">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="O668" s="2"/>
       <c r="P668" t="s" s="2">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="Q668" t="s" s="2">
         <v>21</v>
@@ -76475,7 +76468,7 @@
         <v>21</v>
       </c>
       <c r="AG668" t="s" s="2">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="AH668" t="s" s="2">
         <v>76</v>
@@ -76492,13 +76485,13 @@
     </row>
     <row r="669">
       <c r="A669" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="C669" t="s" s="2">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="D669" s="2"/>
       <c r="E669" t="s" s="2">
@@ -76521,17 +76514,17 @@
         <v>21</v>
       </c>
       <c r="L669" t="s" s="2">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="M669" t="s" s="2">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="N669" t="s" s="2">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="O669" s="2"/>
       <c r="P669" t="s" s="2">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="Q669" t="s" s="2">
         <v>21</v>
@@ -76580,7 +76573,7 @@
         <v>21</v>
       </c>
       <c r="AG669" t="s" s="2">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="AH669" t="s" s="2">
         <v>76</v>
@@ -76597,13 +76590,13 @@
     </row>
     <row r="670">
       <c r="A670" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B670" t="s" s="2">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="C670" t="s" s="2">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="D670" s="2"/>
       <c r="E670" t="s" s="2">
@@ -76629,10 +76622,10 @@
         <v>351</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="N670" t="s" s="2">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="O670" s="2"/>
       <c r="P670" s="2"/>
@@ -76683,7 +76676,7 @@
         <v>21</v>
       </c>
       <c r="AG670" t="s" s="2">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="AH670" t="s" s="2">
         <v>76</v>
@@ -76700,13 +76693,13 @@
     </row>
     <row r="671">
       <c r="A671" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B671" t="s" s="2">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="C671" t="s" s="2">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="D671" s="2"/>
       <c r="E671" t="s" s="2">
@@ -76803,13 +76796,13 @@
     </row>
     <row r="672">
       <c r="A672" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B672" t="s" s="2">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="C672" t="s" s="2">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="D672" s="2"/>
       <c r="E672" t="s" s="2">
@@ -76908,13 +76901,13 @@
     </row>
     <row r="673">
       <c r="A673" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B673" t="s" s="2">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="C673" t="s" s="2">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="D673" s="2"/>
       <c r="E673" t="s" s="2">
@@ -77015,13 +77008,13 @@
     </row>
     <row r="674">
       <c r="A674" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B674" t="s" s="2">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="C674" t="s" s="2">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="D674" s="2"/>
       <c r="E674" t="s" s="2">
@@ -77047,14 +77040,14 @@
         <v>222</v>
       </c>
       <c r="M674" t="s" s="2">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="N674" t="s" s="2">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="O674" s="2"/>
       <c r="P674" t="s" s="2">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="Q674" t="s" s="2">
         <v>21</v>
@@ -77103,7 +77096,7 @@
         <v>21</v>
       </c>
       <c r="AG674" t="s" s="2">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="AH674" t="s" s="2">
         <v>76</v>
@@ -77120,13 +77113,13 @@
     </row>
     <row r="675">
       <c r="A675" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B675" t="s" s="2">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="C675" t="s" s="2">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="D675" s="2"/>
       <c r="E675" t="s" s="2">
@@ -77152,10 +77145,10 @@
         <v>238</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="N675" t="s" s="2">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="O675" s="2"/>
       <c r="P675" s="2"/>
@@ -77186,7 +77179,7 @@
       </c>
       <c r="Z675" s="2"/>
       <c r="AA675" t="s" s="2">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="AB675" t="s" s="2">
         <v>21</v>
@@ -77204,7 +77197,7 @@
         <v>21</v>
       </c>
       <c r="AG675" t="s" s="2">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="AH675" t="s" s="2">
         <v>82</v>
@@ -77221,13 +77214,13 @@
     </row>
     <row r="676">
       <c r="A676" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B676" t="s" s="2">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="C676" t="s" s="2">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="D676" s="2"/>
       <c r="E676" t="s" s="2">
@@ -77253,14 +77246,14 @@
         <v>262</v>
       </c>
       <c r="M676" t="s" s="2">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="N676" t="s" s="2">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="O676" s="2"/>
       <c r="P676" t="s" s="2">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="Q676" t="s" s="2">
         <v>21</v>
@@ -77309,7 +77302,7 @@
         <v>21</v>
       </c>
       <c r="AG676" t="s" s="2">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="AH676" t="s" s="2">
         <v>76</v>
@@ -77326,13 +77319,13 @@
     </row>
     <row r="677">
       <c r="A677" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C677" t="s" s="2">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="D677" s="2"/>
       <c r="E677" t="s" s="2">
@@ -77358,10 +77351,10 @@
         <v>267</v>
       </c>
       <c r="M677" t="s" s="2">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="N677" t="s" s="2">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="O677" s="2"/>
       <c r="P677" s="2"/>
@@ -77412,7 +77405,7 @@
         <v>21</v>
       </c>
       <c r="AG677" t="s" s="2">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="AH677" t="s" s="2">
         <v>76</v>
@@ -77429,13 +77422,13 @@
     </row>
     <row r="678">
       <c r="A678" t="s" s="2">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C678" t="s" s="2">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="D678" s="2"/>
       <c r="E678" t="s" s="2">
@@ -77461,16 +77454,16 @@
         <v>238</v>
       </c>
       <c r="M678" t="s" s="2">
+        <v>1673</v>
+      </c>
+      <c r="N678" t="s" s="2">
+        <v>1674</v>
+      </c>
+      <c r="O678" t="s" s="2">
         <v>1675</v>
       </c>
-      <c r="N678" t="s" s="2">
+      <c r="P678" t="s" s="2">
         <v>1676</v>
-      </c>
-      <c r="O678" t="s" s="2">
-        <v>1677</v>
-      </c>
-      <c r="P678" t="s" s="2">
-        <v>1678</v>
       </c>
       <c r="Q678" t="s" s="2">
         <v>21</v>
@@ -77519,7 +77512,7 @@
         <v>21</v>
       </c>
       <c r="AG678" t="s" s="2">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="AH678" t="s" s="2">
         <v>76</v>

--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T17:02:42+02:00</t>
+    <t>2026-10-15T08:29:54+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
